--- a/artfynd/A 17079-2022 artfynd.xlsx
+++ b/artfynd/A 17079-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129012160</v>
       </c>
       <c r="B2" t="n">
-        <v>107160</v>
+        <v>107165</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17079-2022 artfynd.xlsx
+++ b/artfynd/A 17079-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129012160</v>
       </c>
       <c r="B2" t="n">
-        <v>107165</v>
+        <v>107168</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Malin Schött, Denise Gunnarsson, Elvira Ljungberg</t>
+          <t>Elvira Ljungberg, Denise Gunnarsson, Malin Schött</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 17079-2022 artfynd.xlsx
+++ b/artfynd/A 17079-2022 artfynd.xlsx
@@ -779,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elvira Ljungberg, Denise Gunnarsson, Malin Schött</t>
+          <t>Malin Schött, Denise Gunnarsson, Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 17079-2022 artfynd.xlsx
+++ b/artfynd/A 17079-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129012160</v>
       </c>
       <c r="B2" t="n">
-        <v>107168</v>
+        <v>107178</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17079-2022 artfynd.xlsx
+++ b/artfynd/A 17079-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129012160</v>
       </c>
       <c r="B2" t="n">
-        <v>107178</v>
+        <v>107185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17079-2022 artfynd.xlsx
+++ b/artfynd/A 17079-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129012160</v>
       </c>
       <c r="B2" t="n">
-        <v>107185</v>
+        <v>107187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17079-2022 artfynd.xlsx
+++ b/artfynd/A 17079-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129012160</v>
       </c>
       <c r="B2" t="n">
-        <v>107187</v>
+        <v>107213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17079-2022 artfynd.xlsx
+++ b/artfynd/A 17079-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129012160</v>
       </c>
       <c r="B2" t="n">
-        <v>107213</v>
+        <v>107215</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17079-2022 artfynd.xlsx
+++ b/artfynd/A 17079-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129012160</v>
       </c>
       <c r="B2" t="n">
-        <v>107215</v>
+        <v>107216</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17079-2022 artfynd.xlsx
+++ b/artfynd/A 17079-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129012160</v>
       </c>
       <c r="B2" t="n">
-        <v>107216</v>
+        <v>107220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17079-2022 artfynd.xlsx
+++ b/artfynd/A 17079-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129012160</v>
       </c>
       <c r="B2" t="n">
-        <v>107239</v>
+        <v>107707</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
